--- a/AAII_Financials/Quarterly/NVNI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NVNI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="92">
   <si>
     <t>NVNI</t>
   </si>
@@ -656,62 +656,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
@@ -727,38 +729,44 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F8" s="3">
         <v>8900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>9200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>9000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>8600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>8200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>9300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>8300</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
@@ -774,8 +782,14 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -783,28 +797,28 @@
         <v>3000</v>
       </c>
       <c r="E9" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G9" s="3">
         <v>3100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>3300</v>
-      </c>
-      <c r="G9" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H9" s="3">
-        <v>2800</v>
       </c>
       <c r="I9" s="3">
         <v>3200</v>
       </c>
       <c r="J9" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K9" s="3">
         <v>3200</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
+      <c r="L9" s="3">
+        <v>3200</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
@@ -821,38 +835,44 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>6400</v>
+      </c>
+      <c r="F10" s="3">
         <v>6000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>6200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>5700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>5400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>5400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>6100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>5100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -868,8 +888,14 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -887,35 +913,37 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
         <v>800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>900</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3">
         <v>800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>900</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -934,8 +962,14 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -981,38 +1015,44 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>100</v>
+      </c>
+      <c r="F14" s="3">
         <v>1400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>1500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>2700</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1028,43 +1068,49 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>900</v>
+      </c>
+      <c r="F15" s="3">
         <v>400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>900</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>3</v>
@@ -1075,8 +1121,14 @@
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1091,38 +1143,40 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F17" s="3">
         <v>8500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>8800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>11900</v>
       </c>
-      <c r="G17" s="3">
-        <v>11300</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>11400</v>
+      </c>
+      <c r="J17" s="3">
         <v>6500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>7400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>7000</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1138,38 +1192,44 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F18" s="3">
         <v>400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-2900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-2800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>1700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1300</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1185,8 +1245,14 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1204,38 +1270,40 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>600</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1251,43 +1319,49 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F21" s="3">
         <v>700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-1200</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I21" s="3">
-        <v>1900</v>
       </c>
       <c r="J21" s="3">
         <v>1600</v>
       </c>
       <c r="K21" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
+        <v>1600</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
+        <v>0</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
@@ -1298,38 +1372,44 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="E22" s="3">
         <v>2900</v>
       </c>
       <c r="F22" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H22" s="3">
         <v>2700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>2600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>5300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>6000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>600</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1345,38 +1425,44 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-4000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-4100</v>
       </c>
-      <c r="F23" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="I23" s="3">
         <v>-4600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-3300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-3700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2500</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1392,8 +1478,14 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1404,10 +1496,10 @@
         <v>600</v>
       </c>
       <c r="F24" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="G24" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="H24" s="3">
         <v>400</v>
@@ -1416,14 +1508,14 @@
         <v>400</v>
       </c>
       <c r="J24" s="3">
+        <v>400</v>
+      </c>
+      <c r="K24" s="3">
+        <v>400</v>
+      </c>
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1439,8 +1531,14 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1486,38 +1584,44 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-4500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-4700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-5300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-5000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-3600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-4100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-3000</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1533,38 +1637,44 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-5000</v>
-      </c>
-      <c r="E27" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-5400</v>
       </c>
       <c r="G27" s="3">
         <v>-5100</v>
       </c>
       <c r="H27" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="J27" s="3">
         <v>-3900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-4500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-3400</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1580,8 +1690,14 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1627,23 +1743,29 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-300</v>
       </c>
-      <c r="E29" s="3">
+      <c r="G29" s="3">
         <v>-300</v>
       </c>
-      <c r="F29" s="3">
-        <v>300</v>
-      </c>
-      <c r="G29" s="3">
-        <v>300</v>
-      </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
@@ -1659,11 +1781,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>3</v>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>3</v>
@@ -1674,8 +1796,14 @@
       <c r="Q29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1721,8 +1849,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1768,38 +1902,44 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>400</v>
+      </c>
+      <c r="E32" s="3">
+        <v>400</v>
+      </c>
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-600</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1815,38 +1955,44 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-5000</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-5400</v>
       </c>
       <c r="G33" s="3">
         <v>-5100</v>
       </c>
       <c r="H33" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="J33" s="3">
         <v>-3900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-4500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-3400</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1862,8 +2008,14 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1909,38 +2061,44 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-5000</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-5400</v>
       </c>
       <c r="G35" s="3">
         <v>-5100</v>
       </c>
       <c r="H35" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="J35" s="3">
         <v>-3900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-4500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-3400</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1956,43 +2114,49 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2008,8 +2172,14 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2027,8 +2197,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2046,35 +2218,37 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F41" s="3">
         <v>2400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3300</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2093,8 +2267,14 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2125,11 +2305,11 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
@@ -2140,35 +2320,41 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F43" s="3">
         <v>3100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>3200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2900</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2187,8 +2373,14 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2234,35 +2426,41 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F45" s="3">
         <v>5600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>5800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>6300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>6000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>5600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>6300</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2281,8 +2479,14 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2290,26 +2494,26 @@
         <v>11100</v>
       </c>
       <c r="E46" s="3">
+        <v>11100</v>
+      </c>
+      <c r="F46" s="3">
+        <v>11100</v>
+      </c>
+      <c r="G46" s="3">
         <v>11500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>11500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>10900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>11000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>12500</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2328,8 +2532,14 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2375,16 +2585,22 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="E48" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="F48" s="3">
         <v>1100</v>
@@ -2393,17 +2609,17 @@
         <v>1100</v>
       </c>
       <c r="H48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J48" s="3">
         <v>1000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1200</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2422,37 +2638,43 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>50500</v>
+      </c>
+      <c r="F49" s="3">
         <v>48900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>50600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>53200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>50500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>51600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>58700</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2469,8 +2691,14 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2516,8 +2744,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2563,35 +2797,41 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E52" s="3">
         <v>2000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G52" s="3">
         <v>2100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2100</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2610,8 +2850,14 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2657,35 +2903,41 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>64600</v>
+      </c>
+      <c r="F54" s="3">
         <v>63100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>65200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>67300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>64000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>65500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>74400</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2704,8 +2956,14 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2723,8 +2981,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2742,35 +3002,37 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F57" s="3">
         <v>10300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>10700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>8800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>8300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>9900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>11300</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2789,37 +3051,43 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F58" s="3">
         <v>6100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>6400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>4200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>4000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>7300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>8300</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
@@ -2836,35 +3104,41 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>59800</v>
+      </c>
+      <c r="F59" s="3">
         <v>53200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>55000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>50900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>48400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>46300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>52600</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2883,35 +3157,41 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>81300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>80800</v>
+      </c>
+      <c r="F60" s="3">
         <v>74400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>76900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>69100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>65600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>67400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>76500</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2930,43 +3210,49 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7300</v>
+      </c>
+      <c r="F61" s="3">
         <v>5400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>5600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>4600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>4400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>3800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>4300</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N61" s="3" t="s">
-        <v>3</v>
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
       </c>
       <c r="O61" s="3" t="s">
         <v>3</v>
@@ -2977,35 +3263,41 @@
       <c r="Q61" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S61" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F62" s="3">
         <v>5000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>5100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>5200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>4900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>5900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>6700</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3024,8 +3316,14 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3071,8 +3369,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3118,8 +3422,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3165,35 +3475,41 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>99100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>98400</v>
+      </c>
+      <c r="F66" s="3">
         <v>91200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>94300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>85700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>81400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>83600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>94900</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3212,8 +3528,14 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3231,8 +3553,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3278,8 +3602,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3325,8 +3655,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3357,11 +3693,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N70" s="3" t="s">
-        <v>3</v>
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
+        <v>0</v>
       </c>
       <c r="O70" s="3" t="s">
         <v>3</v>
@@ -3372,8 +3708,14 @@
       <c r="Q70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3419,35 +3761,41 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-127000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-126200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-115800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-119700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-107900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-102600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-85700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-97300</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3466,8 +3814,14 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3513,8 +3867,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3560,8 +3920,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3607,35 +3973,41 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-32600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="F76" s="3">
         <v>-27100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-28000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-18500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-17500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-19500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-22100</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3654,8 +4026,14 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3701,43 +4079,49 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3753,38 +4137,44 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-5000</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-5400</v>
       </c>
       <c r="G81" s="3">
         <v>-5100</v>
       </c>
       <c r="H81" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="J81" s="3">
         <v>-3900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-4500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-3400</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3800,8 +4190,14 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3819,29 +4215,31 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>900</v>
+      </c>
+      <c r="E83" s="3">
+        <v>900</v>
+      </c>
+      <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1000</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,8 +4264,14 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3913,8 +4317,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3960,8 +4370,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4007,8 +4423,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4054,8 +4476,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4101,38 +4529,44 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F89" s="3">
         <v>3700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>3800</v>
       </c>
-      <c r="F89" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-2800</v>
-      </c>
       <c r="H89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J89" s="3">
         <v>1700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>1600</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4148,8 +4582,14 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4167,8 +4607,10 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4179,10 +4621,10 @@
         <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
@@ -4193,11 +4635,11 @@
       <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
+      <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-100</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
@@ -4214,8 +4656,14 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4261,8 +4709,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4308,37 +4762,43 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-3200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-3300</v>
       </c>
-      <c r="F94" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G94" s="3">
-        <v>2300</v>
-      </c>
       <c r="H94" s="3">
-        <v>-700</v>
+        <v>-400</v>
       </c>
       <c r="I94" s="3">
-        <v>-800</v>
+        <v>-400</v>
       </c>
       <c r="J94" s="3">
         <v>-700</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
+      <c r="K94" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L94" s="3">
+        <v>-700</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
@@ -4355,8 +4815,14 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4374,8 +4840,10 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4421,8 +4889,14 @@
       <c r="Q96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4468,8 +4942,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4515,8 +4995,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4562,37 +5048,43 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>1100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>1100</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-700</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-800</v>
       </c>
       <c r="J100" s="3">
         <v>-700</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
+      <c r="K100" s="3">
+        <v>-800</v>
+      </c>
+      <c r="L100" s="3">
+        <v>-700</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
@@ -4609,16 +5101,22 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-700</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -4656,43 +5154,49 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="E102" s="3">
         <v>-300</v>
       </c>
       <c r="F102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H102" s="3">
         <v>-200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>200</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
@@ -4701,6 +5205,12 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
